--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484583_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484583_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.498</v>
+        <v>1.57</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0169</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4811</v>
+        <v>0.7288</v>
       </c>
       <c r="G3" t="n">
         <v>-1.6198</v>
@@ -688,13 +688,13 @@
         <v>3.1154</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3379</v>
+        <v>-0.2658</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.23</v>
+        <v>-0.4057</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1079</v>
+        <v>0.1399</v>
       </c>
       <c r="V3" t="n">
         <v>1.2566</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0329</v>
+        <v>-0.3517</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6092</v>
+        <v>1.2246</v>
       </c>
       <c r="F4" t="n">
         <v>-1.5764</v>
@@ -766,10 +766,10 @@
         <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1644</v>
+        <v>-0.2202</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4563</v>
+        <v>0.0717</v>
       </c>
       <c r="U4" t="n">
         <v>-0.2919</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CHALATASHVILI</t>
+          <t>J. REY SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6097</v>
+        <v>-0.4248</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1769</v>
+        <v>-1.6033</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4328</v>
+        <v>1.1785</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4941</v>
+        <v>-0.4062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2112</v>
+        <v>2.2864</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7053</v>
+        <v>-2.6926</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0433</v>
+        <v>-0.3967</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0433</v>
+        <v>1.5264</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.9231</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5374</v>
+        <v>-0.0095</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1679</v>
+        <v>0.76</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7053</v>
+        <v>-0.7695</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2989</v>
+        <v>-0.8196</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2202</v>
+        <v>-0.3582</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.4614</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. REY SANCHEZ</t>
+          <t>D. CHALATASHVILI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7906</v>
+        <v>-0.5353</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7956</v>
+        <v>-0.1769</v>
       </c>
       <c r="F6" t="n">
-        <v>1.005</v>
+        <v>-0.3585</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4062</v>
+        <v>-0.4941</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2864</v>
+        <v>0.2112</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6926</v>
+        <v>-0.7053</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3967</v>
+        <v>0.0433</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5264</v>
+        <v>0.0433</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9231</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0095</v>
+        <v>-0.5374</v>
       </c>
       <c r="N6" t="n">
-        <v>0.76</v>
+        <v>0.1679</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7695</v>
+        <v>-0.7053</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1853</v>
+        <v>-0.2245</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5505</v>
+        <v>-0.2202</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6348</v>
+        <v>-0.0043</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9084</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7681</v>
+        <v>-1.7542</v>
       </c>
       <c r="F7" t="n">
-        <v>0.821</v>
+        <v>0.8458</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6123</v>
@@ -1000,13 +1000,13 @@
         <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6756</v>
+        <v>0.7144</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2368</v>
+        <v>0.2508</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4388</v>
+        <v>0.4636</v>
       </c>
       <c r="V7" t="n">
         <v>-0.0104</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. FORNER LUCEA</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4589</v>
+        <v>-1.3161</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6791</v>
+        <v>-0.1735</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2202</v>
+        <v>-1.1426</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8325</v>
+        <v>-1.3274</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.903</v>
+        <v>0.7245</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9296</v>
+        <v>-2.0519</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2387</v>
+        <v>0.9596</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5977</v>
+        <v>0.9596</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.641</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5938</v>
+        <v>-2.287</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3053</v>
+        <v>-0.2351</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2885</v>
+        <v>-2.0519</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1833</v>
+        <v>1.4661</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5569</v>
+        <v>-0.1878</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4759</v>
+        <v>-0.2168</v>
       </c>
       <c r="U8" t="n">
-        <v>0.081</v>
+        <v>0.029</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>O. FORNER LUCEA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5885</v>
+        <v>-1.7914</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6926</v>
+        <v>-1.9125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1041</v>
+        <v>0.1211</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8122</v>
+        <v>-1.8325</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.95</v>
+        <v>-0.903</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1378</v>
+        <v>-0.9296</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2335</v>
+        <v>-1.2387</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1918</v>
+        <v>-0.5977</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0417</v>
+        <v>-0.641</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0457</v>
+        <v>-0.5938</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1418</v>
+        <v>-0.3053</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0961</v>
+        <v>-0.2885</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1991</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4229</v>
+        <v>0.2244</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8228</v>
+        <v>0.2425</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6001</v>
+        <v>-0.0181</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6314</v>
+        <v>-2.1322</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4777</v>
+        <v>-2.3106</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1091</v>
+        <v>0.1785</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6418</v>
+        <v>-0.8122</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4967</v>
+        <v>-0.95</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1384</v>
+        <v>0.1378</v>
       </c>
       <c r="J10" t="n">
-        <v>1.088</v>
+        <v>0.2335</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0463</v>
+        <v>0.1918</v>
       </c>
       <c r="L10" t="n">
         <v>0.0417</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7297</v>
+        <v>-1.0457</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5496</v>
+        <v>-1.1418</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1801</v>
+        <v>0.0961</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3665</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R10" t="n">
-        <v>3.2986</v>
+        <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>0.678</v>
+        <v>0.8792</v>
       </c>
       <c r="T10" t="n">
-        <v>0.822</v>
+        <v>0.2048</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1441</v>
+        <v>0.6744</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2328</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8024</v>
+        <v>-2.5933</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7093</v>
+        <v>-0.2365</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0931</v>
+        <v>-2.3568</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3274</v>
+        <v>-1.6418</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7245</v>
+        <v>0.4967</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0519</v>
+        <v>-2.1384</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9596</v>
+        <v>1.088</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9596</v>
+        <v>1.0463</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.287</v>
+        <v>-2.7297</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2351</v>
+        <v>-0.5496</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0519</v>
+        <v>-2.1801</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4661</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3823</v>
+        <v>3.2986</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6741</v>
+        <v>-0.2839</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7526</v>
+        <v>0.1079</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0786</v>
+        <v>-0.3918</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.267</v>
+        <v>-0.3011</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.2328</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. VANOUKIA</t>
+          <t>L. SALVADOR MONTANES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.936</v>
+        <v>-2.807</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0326</v>
+        <v>-2.2941</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09660000000000001</v>
+        <v>-0.5128</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3543</v>
+        <v>-2.2075</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.0917</v>
+        <v>-0.1429</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2627</v>
+        <v>-2.0646</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.8659</v>
+        <v>1.4548</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.6354</v>
+        <v>2.0124</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2305</v>
+        <v>-0.5577</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4884</v>
+        <v>-3.6623</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4563</v>
+        <v>-2.1554</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0321</v>
+        <v>-1.5069</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4661</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4661</v>
+        <v>2.7489</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5961</v>
+        <v>-0.0051</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1666</v>
+        <v>-0.4057</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7628</v>
+        <v>0.4006</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6439</v>
+        <v>0.3219</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTANES</t>
+          <t>M. VANOUKIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8597</v>
+        <v>-3.2526</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1735</v>
+        <v>-2.9775</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6862</v>
+        <v>-0.275</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2075</v>
+        <v>-4.3543</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1429</v>
+        <v>-3.0917</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.0646</v>
+        <v>-1.2627</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4548</v>
+        <v>-2.8659</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0124</v>
+        <v>-1.6354</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5577</v>
+        <v>-1.2305</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.6623</v>
+        <v>-1.4884</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1554</v>
+        <v>-1.4563</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5069</v>
+        <v>-0.0321</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7489</v>
+        <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0578</v>
+        <v>0.2796</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.285</v>
+        <v>-0.1116</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2272</v>
+        <v>0.3912</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3219</v>
+        <v>-0.6439</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="14">
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.1929</v>
+        <v>-12.6423</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.0234</v>
+        <v>-9.472799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1696</v>
+        <v>-3.1694</v>
       </c>
       <c r="G14" t="n">
         <v>-15.8219</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3279</v>
+        <v>1.327899999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-17.1501</v>
       </c>
       <c r="J14" t="n">
-        <v>3.055100000000001</v>
+        <v>3.055099999999999</v>
       </c>
       <c r="K14" t="n">
         <v>9.7849</v>
@@ -1546,13 +1546,13 @@
         <v>19.2421</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4601000000000003</v>
+        <v>0.09069999999999989</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3911</v>
+        <v>-0.8405000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9311</v>
+        <v>0.9312000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.2566</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8369</v>
+        <v>5.5115</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7592</v>
+        <v>3.8553</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0777</v>
+        <v>1.6562</v>
       </c>
       <c r="G15" t="n">
         <v>4.8057</v>
@@ -1624,13 +1624,13 @@
         <v>2.5656</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6835</v>
+        <v>-0.0089</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.405</v>
+        <v>-0.3088</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2785</v>
+        <v>0.2999</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9346</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1456</v>
+        <v>4.147</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5355</v>
+        <v>3.6317</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6101</v>
+        <v>0.5154</v>
       </c>
       <c r="G16" t="n">
         <v>4.3592</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7328</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1116</v>
+        <v>-0.0154</v>
       </c>
       <c r="U16" t="n">
-        <v>0.843</v>
+        <v>0.7483</v>
       </c>
       <c r="V16" t="n">
         <v>-0.945</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0833</v>
+        <v>3.4984</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.574</v>
+        <v>-1.0933</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6573</v>
+        <v>4.5917</v>
       </c>
       <c r="G17" t="n">
         <v>2.9638</v>
@@ -1780,13 +1780,13 @@
         <v>3.2986</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4877</v>
+        <v>-0.0726</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3031</v>
+        <v>-0.8224</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8154</v>
+        <v>0.7498</v>
       </c>
       <c r="V17" t="n">
         <v>1.89</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9522</v>
+        <v>3.1036</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1556</v>
+        <v>1.3479</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7966</v>
+        <v>1.7558</v>
       </c>
       <c r="G18" t="n">
         <v>1.9445</v>
@@ -1858,13 +1858,13 @@
         <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0235</v>
+        <v>0.175</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2767</v>
+        <v>-0.0844</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3003</v>
+        <v>0.2594</v>
       </c>
       <c r="V18" t="n">
         <v>1.9005</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9441</v>
+        <v>2.9936</v>
       </c>
       <c r="E19" t="n">
         <v>1.0128</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9313</v>
+        <v>1.9808</v>
       </c>
       <c r="G19" t="n">
         <v>1.6387</v>
@@ -1936,13 +1936,13 @@
         <v>2.0158</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5278</v>
+        <v>0.5773</v>
       </c>
       <c r="T19" t="n">
         <v>0.1818</v>
       </c>
       <c r="U19" t="n">
-        <v>0.346</v>
+        <v>0.3955</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1643</v>
+        <v>2.9744</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7457</v>
+        <v>1.1303</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4186</v>
+        <v>1.8441</v>
       </c>
       <c r="G20" t="n">
         <v>4.7624</v>
@@ -2014,13 +2014,13 @@
         <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.1833</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4774</v>
+        <v>-0.0927</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.516</v>
+        <v>-0.0905</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3581</v>
+        <v>0.8585</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2465</v>
+        <v>0.5734</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1117</v>
+        <v>0.2851</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2303</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9391</v>
+        <v>0.4395</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0249</v>
+        <v>0.3518</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0858</v>
+        <v>0.0877</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6335</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6083</v>
+        <v>-0.4058</v>
       </c>
       <c r="E23" t="n">
         <v>-0.342</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2663</v>
+        <v>-0.0638</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2544</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5372</v>
+        <v>-0.3346</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3854</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1518</v>
+        <v>0.0507</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-1.7693</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.173</v>
+        <v>-2.0384</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3681</v>
+        <v>0.2691</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0653</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>1.894</v>
+        <v>0.9295</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3907</v>
+        <v>0.5253</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5033</v>
+        <v>0.4042</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6335</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6234</v>
+        <v>-2.2286</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5936</v>
+        <v>-2.4013</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0298</v>
+        <v>0.1727</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4375</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8298</v>
+        <v>-0.435</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5875</v>
+        <v>-0.3952</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2423</v>
+        <v>-0.0398</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6231</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5802</v>
+        <v>-4.5336</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.9282</v>
+        <v>-2.832</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.652</v>
+        <v>-1.7016</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9899</v>
@@ -2482,13 +2482,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1243</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0181</v>
+        <v>0.1143</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1424</v>
+        <v>-0.1919</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6335</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>13.1928</v>
+        <v>14.4748</v>
       </c>
       <c r="E27" t="n">
-        <v>3.169599999999998</v>
+        <v>3.169499999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>10.0233</v>
+        <v>11.3055</v>
       </c>
       <c r="G27" t="n">
         <v>15.822</v>
@@ -2560,13 +2560,13 @@
         <v>17.4095</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4599000000000002</v>
+        <v>1.742</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9312000000000001</v>
+        <v>-0.9311000000000004</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3912</v>
+        <v>2.6733</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2565</v>
